--- a/data/raw/GLNPO 2024 Spring/Superior/D100/SU 14 D100 Spring 2024 24GS02I73 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Superior/D100/SU 14 D100 Spring 2024 24GS02I73 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Superior\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Superior\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D810A312-92A4-4402-ADFC-6889637283A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6C0EE0-A4AA-4CCD-8861-164E97EBF8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D4AA0EF-9341-44A8-BAB4-66D3F52D0848}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D4AA0EF-9341-44A8-BAB4-66D3F52D0848}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="31" r:id="rId2"/>
+    <pivotCache cacheId="43" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2948,7 +2948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{727BA6AA-5816-4558-9DE9-C1DE47FC6C61}" name="PivotTable1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{727BA6AA-5816-4558-9DE9-C1DE47FC6C61}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Z12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3377,19 +3377,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7ED3F8B-F632-4FCC-B786-BFA8149FA79E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z134"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3445,7 +3447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3504,7 +3506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3578,7 +3580,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3646,7 +3648,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3711,7 +3713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3779,7 +3781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3844,7 +3846,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -3909,7 +3911,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3980,7 +3982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4042,7 +4044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4113,7 +4115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4187,7 +4189,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4240,7 +4242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4302,7 +4304,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4362,7 +4364,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -4424,7 +4426,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4484,7 +4486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4544,7 +4546,7 @@
       </c>
       <c r="V18" s="6"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4604,7 +4606,7 @@
       </c>
       <c r="V19" s="6"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4663,7 @@
       </c>
       <c r="U20" s="6"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -4714,7 +4716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -4767,7 +4769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -4820,7 +4822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -4873,7 +4875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -4926,7 +4928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -4979,7 +4981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5032,7 +5034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5085,7 +5087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5138,7 +5140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5191,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5244,7 +5246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -5297,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -5350,7 +5352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -5403,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -5456,7 +5458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -5509,7 +5511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -5562,7 +5564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -5615,7 +5617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -5668,7 +5670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -5721,7 +5723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -5774,7 +5776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -5827,7 +5829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -5880,7 +5882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -5927,13 +5929,13 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -5986,7 +5988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6039,7 +6041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6092,7 +6094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6145,7 +6147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6198,7 +6200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6251,7 +6253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6304,7 +6306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6357,7 +6359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -6410,7 +6412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6463,7 +6465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -6516,7 +6518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -6569,7 +6571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6622,7 +6624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -6675,7 +6677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -6728,7 +6730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -6781,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -6834,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -6887,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -6940,7 +6942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -6993,7 +6995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7046,7 +7048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7099,7 +7101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7152,7 +7154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7205,7 +7207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7258,7 +7260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -7311,7 +7313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -7364,7 +7366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -7417,7 +7419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -7470,7 +7472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -7523,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -7576,7 +7578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -7629,7 +7631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -7682,7 +7684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -7735,7 +7737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -7791,7 +7793,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -7844,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -7950,7 +7952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8003,7 +8005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8056,7 +8058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8109,7 +8111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8162,7 +8164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8215,7 +8217,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8268,7 +8270,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -8321,7 +8323,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -8374,7 +8376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -8427,7 +8429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -8480,7 +8482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -8533,7 +8535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -8586,7 +8588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -8639,7 +8641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -8692,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -8745,7 +8747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -8798,7 +8800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -8851,7 +8853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -8904,7 +8906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -8957,7 +8959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9010,7 +9012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9063,7 +9065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9116,7 +9118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9169,7 +9171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9222,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9275,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -9328,7 +9330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -9381,7 +9383,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -9434,7 +9436,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -9487,7 +9489,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -9540,7 +9542,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -9593,7 +9595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -9646,7 +9648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -9699,7 +9701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -9752,7 +9754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -9805,7 +9807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -9858,7 +9860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -9911,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -9964,7 +9966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10017,7 +10019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10070,7 +10072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10123,7 +10125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10176,7 +10178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10229,7 +10231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10282,7 +10284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -10335,7 +10337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -10388,7 +10390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -10441,7 +10443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -10494,7 +10496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -10547,7 +10549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>18</v>
       </c>
@@ -10600,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>18</v>
       </c>
@@ -10653,7 +10655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>18</v>
       </c>
@@ -10707,7 +10709,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R134" xr:uid="{D7ED3F8B-F632-4FCC-B786-BFA8149FA79E}"/>
+  <autoFilter ref="A1:R134" xr:uid="{D7ED3F8B-F632-4FCC-B786-BFA8149FA79E}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Diacyclops thomasi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>